--- a/Documents/S-158-100/2.0.0/WD-158_100_2_0_0_20260831.xlsx
+++ b/Documents/S-158-100/2.0.0/WD-158_100_2_0_0_20260831.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\work\git\S-100-Validation-Checks\Documents\S-158-100\2.0.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08E2BA7B-04D9-4612-837C-C87B66928263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A9D116-4E9B-4A63-9ADA-E3001416C5EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="28110" windowHeight="18240" activeTab="1" xr2:uid="{D500D42E-56ED-44C2-B321-3F3845968AA3}"/>
   </bookViews>
@@ -10203,6 +10203,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -10221,9 +10224,6 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -10577,14 +10577,14 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15.75" thickBot="1"/>
     <row r="2" spans="2:8" ht="33.6" customHeight="1">
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="77" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="79"/>
       <c r="H2" s="5"/>
     </row>
     <row r="3" spans="2:8" s="4" customFormat="1" ht="20.45" customHeight="1">
@@ -10710,7 +10710,7 @@
       <c r="G12" s="7"/>
     </row>
     <row r="13" spans="2:8" s="4" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B13" s="75" t="s">
+      <c r="B13" s="76" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="22" t="s">
@@ -10724,7 +10724,7 @@
       <c r="G13" s="7"/>
     </row>
     <row r="14" spans="2:8" s="4" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B14" s="75"/>
+      <c r="B14" s="76"/>
       <c r="C14" s="28"/>
       <c r="D14" s="26"/>
       <c r="E14" s="29"/>
@@ -10732,7 +10732,7 @@
       <c r="G14" s="7"/>
     </row>
     <row r="15" spans="2:8" s="4" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B15" s="75"/>
+      <c r="B15" s="76"/>
       <c r="C15" s="31"/>
       <c r="D15" s="26"/>
       <c r="E15" s="27"/>
@@ -10740,7 +10740,7 @@
       <c r="G15" s="7"/>
     </row>
     <row r="16" spans="2:8" s="4" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B16" s="75"/>
+      <c r="B16" s="76"/>
       <c r="C16" s="20"/>
       <c r="D16" s="6"/>
       <c r="E16" s="19"/>
@@ -10748,7 +10748,7 @@
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="2:7" s="4" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B17" s="75"/>
+      <c r="B17" s="76"/>
       <c r="C17" s="21"/>
       <c r="D17" s="19"/>
       <c r="E17" s="19"/>
@@ -10756,7 +10756,7 @@
       <c r="G17" s="7"/>
     </row>
     <row r="18" spans="2:7" s="4" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B18" s="75"/>
+      <c r="B18" s="76"/>
       <c r="C18" s="11"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
@@ -10795,15 +10795,15 @@
   <dimension ref="A1:P355"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
     <col min="2" max="2" width="10.85546875" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" style="37" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="37" customWidth="1"/>
     <col min="4" max="4" width="31.7109375" style="35" customWidth="1"/>
     <col min="5" max="5" width="53.85546875" style="35" customWidth="1"/>
     <col min="6" max="6" width="34.140625" style="35" customWidth="1"/>
     <col min="7" max="7" width="18.85546875" customWidth="1"/>
     <col min="8" max="8" width="13.85546875" style="34" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" style="34" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" style="34" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
     <col min="11" max="11" width="10.5703125" customWidth="1"/>
     <col min="13" max="13" width="55.140625" style="36" customWidth="1"/>
@@ -10873,7 +10873,7 @@
       <c r="D2" s="35" t="s">
         <v>804</v>
       </c>
-      <c r="E2" s="82" t="s">
+      <c r="E2" s="75" t="s">
         <v>1943</v>
       </c>
       <c r="F2" s="35" t="s">
@@ -22812,10 +22812,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="80" t="s">
         <v>1672</v>
       </c>
-      <c r="B1" s="79"/>
+      <c r="B1" s="80"/>
     </row>
     <row r="2" spans="1:2" ht="30">
       <c r="B2" s="34" t="s">
@@ -22823,10 +22823,10 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="80" t="s">
         <v>1659</v>
       </c>
-      <c r="B3" s="79"/>
+      <c r="B3" s="80"/>
     </row>
     <row r="4" spans="1:2">
       <c r="B4" s="34" t="s">
@@ -22869,10 +22869,10 @@
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="79" t="s">
+      <c r="A12" s="80" t="s">
         <v>1675</v>
       </c>
-      <c r="B12" s="79"/>
+      <c r="B12" s="80"/>
     </row>
     <row r="13" spans="1:2" ht="30">
       <c r="B13" s="34" t="s">
@@ -22885,10 +22885,10 @@
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="79" t="s">
+      <c r="A15" s="80" t="s">
         <v>1669</v>
       </c>
-      <c r="B15" s="79"/>
+      <c r="B15" s="80"/>
     </row>
     <row r="16" spans="1:2">
       <c r="B16" s="34" t="s">
@@ -22938,10 +22938,10 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="80">
+      <c r="A2" s="81">
         <v>2</v>
       </c>
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="81" t="s">
         <v>1845</v>
       </c>
       <c r="C2" s="68" t="s">
@@ -22952,8 +22952,8 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="80"/>
-      <c r="B3" s="80"/>
+      <c r="A3" s="81"/>
+      <c r="B3" s="81"/>
       <c r="C3" s="68" t="s">
         <v>1852</v>
       </c>
@@ -22962,8 +22962,8 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="80"/>
-      <c r="B4" s="80">
+      <c r="A4" s="81"/>
+      <c r="B4" s="81">
         <v>5</v>
       </c>
       <c r="C4" s="68" t="s">
@@ -22974,8 +22974,8 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="80"/>
-      <c r="B5" s="80"/>
+      <c r="A5" s="81"/>
+      <c r="B5" s="81"/>
       <c r="C5" s="68" t="s">
         <v>1852</v>
       </c>
@@ -22984,7 +22984,7 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="80" t="s">
+      <c r="A6" s="81" t="s">
         <v>1848</v>
       </c>
       <c r="B6" s="68" t="s">
@@ -22998,7 +22998,7 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="80"/>
+      <c r="A7" s="81"/>
       <c r="B7" s="68" t="s">
         <v>1849</v>
       </c>
@@ -23018,12 +23018,12 @@
       </c>
     </row>
     <row r="10" spans="1:4" ht="45" customHeight="1">
-      <c r="A10" s="81" t="s">
+      <c r="A10" s="82" t="s">
         <v>1861</v>
       </c>
-      <c r="B10" s="81"/>
-      <c r="C10" s="81"/>
-      <c r="D10" s="81"/>
+      <c r="B10" s="82"/>
+      <c r="C10" s="82"/>
+      <c r="D10" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -23067,10 +23067,10 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="80">
+      <c r="A2" s="81">
         <v>2</v>
       </c>
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="81" t="s">
         <v>1845</v>
       </c>
       <c r="C2" s="68" t="s">
@@ -23084,8 +23084,8 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="80"/>
-      <c r="B3" s="80"/>
+      <c r="A3" s="81"/>
+      <c r="B3" s="81"/>
       <c r="C3" s="68" t="s">
         <v>1852</v>
       </c>
@@ -23097,8 +23097,8 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="80"/>
-      <c r="B4" s="80">
+      <c r="A4" s="81"/>
+      <c r="B4" s="81">
         <v>5</v>
       </c>
       <c r="C4" s="68" t="s">
@@ -23112,8 +23112,8 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="80"/>
-      <c r="B5" s="80"/>
+      <c r="A5" s="81"/>
+      <c r="B5" s="81"/>
       <c r="C5" s="68" t="s">
         <v>1852</v>
       </c>
@@ -23125,7 +23125,7 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="80" t="s">
+      <c r="A6" s="81" t="s">
         <v>1848</v>
       </c>
       <c r="B6" s="68" t="s">
@@ -23142,7 +23142,7 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="80"/>
+      <c r="A7" s="81"/>
       <c r="B7" s="68" t="s">
         <v>1849</v>
       </c>
@@ -23165,12 +23165,12 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="45" customHeight="1">
-      <c r="A12" s="81" t="s">
+      <c r="A12" s="82" t="s">
         <v>1861</v>
       </c>
-      <c r="B12" s="81"/>
-      <c r="C12" s="81"/>
-      <c r="D12" s="81"/>
+      <c r="B12" s="82"/>
+      <c r="C12" s="82"/>
+      <c r="D12" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="5">
